--- a/TDD_examples/CASE_2_ENEA_HTS_CICC/conductor_1_coupling.xlsx
+++ b/TDD_examples/CASE_2_ENEA_HTS_CICC/conductor_1_coupling.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="contact_perimeter_flag" sheetId="8" r:id="Rc5edd7587d8e4b5b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="contact_perimeter" sheetId="1" r:id="Rbb183f2512464bf3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HTC_choice" sheetId="4" r:id="R66f6e166098546fd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="contact_HTC" sheetId="2" r:id="R87907cdef66749ea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="thermal_contact_resistance" sheetId="12" r:id="R5fc2457c775945ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HTC_multiplier" sheetId="5" r:id="Rbb2d1f9bfdc44f6d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="electric_conductance_mode" sheetId="10" r:id="R92681eaceeec4fa0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="electric_conductance" sheetId="11" r:id="R917bec4e8b64417e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="open_perimeter_fract" sheetId="3" r:id="Rbe2953c6e4024193"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="interf_thickness" sheetId="7" r:id="R2825d5414e764e96"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="trans_transp_multiplier" sheetId="6" r:id="Rb0121e441c3c4614"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="view_factors" sheetId="9" r:id="R5af66a0c22644abe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="contact_perimeter_flag" sheetId="8" r:id="Rc9bb896ed9504286"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="contact_perimeter" sheetId="1" r:id="Rfd6b8d8ace834a94"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HTC_choice" sheetId="4" r:id="R8fa51783d4c44acf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="contact_HTC" sheetId="2" r:id="R016e776efa57417c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="thermal_contact_resistance" sheetId="12" r:id="Re4bbdb032ca744f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HTC_multiplier" sheetId="5" r:id="Rfe024696b0d04f80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="electric_conductance_mode" sheetId="10" r:id="R794b9499faea4e0b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="electric_conductance" sheetId="11" r:id="R165a9fdb49214313"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="open_perimeter_fract" sheetId="3" r:id="R75a0eb0ddaef46ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="interf_thickness" sheetId="7" r:id="Rda02e4f43a614234"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="trans_transp_multiplier" sheetId="6" r:id="R1e63ac1b1f0f42ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="view_factors" sheetId="9" r:id="Rdc10fca87193448f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -25101,7 +25101,7 @@
       <x:c r="A1"/>
       <x:c r="B1"/>
       <x:c r="C1" s="5" t="str">
-        <x:v>%[] flag to define the model to compute the HTC (yellow cells are those to thake into account). flag to decide how to evaluate interface htc.</x:v>
+        <x:v>%[] Flag used to select the HTC model (yellow cells are taken into account). This flag determines how the interface HTC is evaluated.</x:v>
       </x:c>
       <x:c r="D1" s="5"/>
       <x:c r="E1" s="5"/>
@@ -34987,7 +34987,7 @@
       <x:c r="A1"/>
       <x:c r="B1"/>
       <x:c r="C1" t="str">
-        <x:v>[m2K/W] thermal contact resistance between soldi component, should be &gt;= 0; used if flag HTC_choice is 1</x:v>
+        <x:v>[m2 K/W] Thermal contact resistance between solid components; it must be &gt;= 0. Used if HTC_choice is 1.</x:v>
       </x:c>
       <x:c r="D1"/>
       <x:c r="E1"/>
@@ -44870,7 +44870,7 @@
       <x:c r="A1"/>
       <x:c r="B1"/>
       <x:c r="C1" t="str">
-        <x:v>Flag to specify the kind of electric conductance: 1 conductance per unit length (the contact is along a line as for tow cilinder); 2 = actual conductance between components.</x:v>
+        <x:v>Flag used to specify the electric conductance: 1 = conductance per unit length (the contact is along a line, as for two cylinders); 2 = actual conductance between components.</x:v>
       </x:c>
       <x:c r="D1"/>
       <x:c r="E1"/>
